--- a/.yuleosh/reports/layer2-report.xlsx
+++ b/.yuleosh/reports/layer2-report.xlsx
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
     </row>
@@ -631,14 +631,10 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>No integration tests</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
